--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484657_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484657_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3181</v>
+        <v>4.5462</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7791</v>
+        <v>6.0815</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.461</v>
+        <v>-1.5353</v>
       </c>
       <c r="G2" t="n">
         <v>6.0788</v>
@@ -610,13 +610,13 @@
         <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.5775</v>
+        <v>-2.3494</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7722</v>
+        <v>-0.4698</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.8052</v>
+        <v>-1.8796</v>
       </c>
       <c r="V2" t="n">
         <v>0.6335</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5261</v>
+        <v>1.4031</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3485</v>
+        <v>1.9778</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8224</v>
+        <v>-0.5747</v>
       </c>
       <c r="G3" t="n">
         <v>3.9348</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0264</v>
+        <v>-1.1493</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5475</v>
+        <v>0.1769</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.5739</v>
+        <v>-1.3262</v>
       </c>
       <c r="V3" t="n">
         <v>0.6335</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6957</v>
+        <v>0.6475</v>
       </c>
       <c r="E4" t="n">
-        <v>0.652</v>
+        <v>-0.274</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0436</v>
+        <v>0.9216</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0947</v>
+        <v>1.518</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8192</v>
+        <v>-0.5944</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2755</v>
+        <v>2.1124</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9839</v>
+        <v>1.4403</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5415</v>
+        <v>0.065</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5577</v>
+        <v>1.3753</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1109</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2777</v>
+        <v>-0.6594</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.7371</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0354</v>
+        <v>-0.2474</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5845</v>
+        <v>-0.175</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5491</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.5339</v>
+        <v>-0.6231</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>R. RAMOS SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3561</v>
+        <v>0.3856</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4663</v>
+        <v>1.3707</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8225</v>
+        <v>-0.9851</v>
       </c>
       <c r="G5" t="n">
-        <v>1.518</v>
+        <v>0.962</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5944</v>
+        <v>-3.1285</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1124</v>
+        <v>4.0904</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4403</v>
+        <v>2.1652</v>
       </c>
       <c r="K5" t="n">
-        <v>0.065</v>
+        <v>-0.5793</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3753</v>
+        <v>2.7444</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07770000000000001</v>
+        <v>-1.2032</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6594</v>
+        <v>-2.5492</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7371</v>
+        <v>1.346</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-2.4089</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3673</v>
+        <v>-0.7945</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1715</v>
+        <v>-1.6145</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. RAMOS SAN SEBASTIAN</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1313</v>
+        <v>0.047</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0272</v>
+        <v>0.2263</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1585</v>
+        <v>-0.1793</v>
       </c>
       <c r="G6" t="n">
-        <v>0.962</v>
+        <v>2.0947</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.1285</v>
+        <v>1.8192</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0904</v>
+        <v>0.2755</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1652</v>
+        <v>0.9839</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5793</v>
+        <v>1.5415</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7444</v>
+        <v>-0.5577</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2032</v>
+        <v>1.1109</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.5492</v>
+        <v>0.2777</v>
       </c>
       <c r="O6" t="n">
-        <v>1.346</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8326</v>
+        <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.9259</v>
+        <v>-0.6133</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.138</v>
+        <v>0.1588</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.7879</v>
+        <v>-0.7721</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. HERRANDO CUENCA</t>
+          <t>H. RUEDA RIOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8561</v>
+        <v>-0.9014</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9761</v>
+        <v>-2.1844</v>
       </c>
       <c r="F8" t="n">
-        <v>1.12</v>
+        <v>1.283</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.085</v>
+        <v>1.5121</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3092</v>
+        <v>0.2071</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2243</v>
+        <v>1.3049</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2604</v>
+        <v>0.9324</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2604</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0871</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1754</v>
+        <v>0.5796</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0489</v>
+        <v>-0.6382</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2243</v>
+        <v>1.2178</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1833</v>
+        <v>-0.733</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4121</v>
+        <v>-1.6804</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2006</v>
+        <v>-0.368</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2115</v>
+        <v>-1.3124</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. RUEDA RIOS</t>
+          <t>S. HERRANDO CUENCA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4649</v>
+        <v>-1.2684</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6241</v>
+        <v>-2.2645</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1592</v>
+        <v>0.9961</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5121</v>
+        <v>-1.085</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2071</v>
+        <v>-1.3092</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3049</v>
+        <v>0.2243</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9324</v>
+        <v>-1.2604</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8453000000000001</v>
+        <v>-1.2604</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0871</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5796</v>
+        <v>0.1754</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6382</v>
+        <v>-0.0489</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2178</v>
+        <v>0.2243</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.733</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.244</v>
+        <v>-0.0002</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8077</v>
+        <v>-0.0878</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4363</v>
+        <v>0.0877</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6356</v>
+        <v>-5.2406</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8297</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.4653</v>
+        <v>-5.8369</v>
       </c>
       <c r="G10" t="n">
         <v>0.9327</v>
@@ -1234,13 +1234,13 @@
         <v>0.5498</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4846</v>
+        <v>-1.0896</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0565</v>
+        <v>-0.29</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.428</v>
+        <v>-0.7996</v>
       </c>
       <c r="V10" t="n">
         <v>-3.8009</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.0238</v>
+        <v>-6.2843</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0489</v>
+        <v>-3.458</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.975</v>
+        <v>-2.8264</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4297</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3376</v>
+        <v>-1.598</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.3088</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4379</v>
+        <v>-1.2892</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5235</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.789099999999999</v>
+        <v>-7.2387</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5094</v>
+        <v>2.06</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.2986</v>
+        <v>-9.2987</v>
       </c>
       <c r="G12" t="n">
         <v>14.2565</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1524000000000007</v>
+        <v>0.1524</v>
       </c>
       <c r="I12" t="n">
         <v>14.104</v>
@@ -1390,13 +1390,13 @@
         <v>12.8279</v>
       </c>
       <c r="S12" t="n">
-        <v>-11.9988</v>
+        <v>-11.448</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.7639</v>
+        <v>-2.2133</v>
       </c>
       <c r="U12" t="n">
-        <v>-9.2347</v>
+        <v>-9.234699999999998</v>
       </c>
       <c r="V12" t="n">
         <v>-8.214399999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1451</v>
+        <v>6.6498</v>
       </c>
       <c r="E13" t="n">
-        <v>7.684</v>
+        <v>7.5186</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5389</v>
+        <v>-0.8688</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3851</v>
+        <v>3.3306</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6796</v>
+        <v>0.8559</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.0646</v>
+        <v>2.4747</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1795</v>
+        <v>5.9824</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7372</v>
+        <v>3.347</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5577</v>
+        <v>2.6353</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.5646</v>
+        <v>-2.6517</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0576</v>
+        <v>-2.4911</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5069</v>
+        <v>-0.1606</v>
       </c>
       <c r="P13" t="n">
+        <v>1.6493</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-0.1833</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-2.0158</v>
       </c>
       <c r="R13" t="n">
         <v>1.8326</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9125</v>
+        <v>2.3034</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3975</v>
+        <v>1.7195</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5151</v>
+        <v>0.5839</v>
       </c>
       <c r="V13" t="n">
-        <v>3.8009</v>
+        <v>-0.6335</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1229</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3219</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.579</v>
+        <v>5.8246</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7494</v>
+        <v>7.1071</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1704</v>
+        <v>-1.2825</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3306</v>
+        <v>-0.3851</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8559</v>
+        <v>1.6796</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4747</v>
+        <v>-2.0646</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9824</v>
+        <v>3.1795</v>
       </c>
       <c r="K14" t="n">
-        <v>3.347</v>
+        <v>3.7372</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6353</v>
+        <v>-0.5577</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.6517</v>
+        <v>-3.5646</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.4911</v>
+        <v>-2.0576</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1606</v>
+        <v>-1.5069</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6493</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="R14" t="n">
         <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2325</v>
+        <v>2.592</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9503</v>
+        <v>1.8205</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2823</v>
+        <v>0.7715</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6335</v>
+        <v>3.8009</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.1229</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1264</v>
+        <v>4.379</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7473</v>
+        <v>1.0743</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3791</v>
+        <v>3.3048</v>
       </c>
       <c r="G15" t="n">
         <v>-1.9122</v>
@@ -1624,13 +1624,13 @@
         <v>2.3823</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8999</v>
+        <v>2.1525</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4344</v>
+        <v>1.7613</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4655</v>
+        <v>0.3912</v>
       </c>
       <c r="V15" t="n">
         <v>2.8559</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8478</v>
+        <v>0.9999</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0183</v>
+        <v>1.8645</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1705</v>
+        <v>-0.8646</v>
       </c>
       <c r="G16" t="n">
         <v>-5.3746</v>
@@ -1702,13 +1702,13 @@
         <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4765</v>
+        <v>2.6286</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2036</v>
+        <v>2.0498</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2728</v>
+        <v>0.5788</v>
       </c>
       <c r="V16" t="n">
         <v>4.1125</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8991</v>
+        <v>0.7577</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9195</v>
+        <v>1.8233</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0204</v>
+        <v>-1.0656</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2947</v>
@@ -1780,13 +1780,13 @@
         <v>0.1833</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7094</v>
+        <v>0.5681</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3839</v>
+        <v>0.2877</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3256</v>
+        <v>0.2803</v>
       </c>
       <c r="V17" t="n">
         <v>0.3011</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8939</v>
+        <v>0.4073</v>
       </c>
       <c r="E18" t="n">
-        <v>0.429</v>
+        <v>0.1405</v>
       </c>
       <c r="F18" t="n">
-        <v>0.465</v>
+        <v>0.2668</v>
       </c>
       <c r="G18" t="n">
         <v>1.4499</v>
@@ -1858,13 +1858,13 @@
         <v>1.8326</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8106</v>
+        <v>1.3239</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0973</v>
+        <v>0.8088</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.5151</v>
       </c>
       <c r="V18" t="n">
         <v>-1.267</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.572</v>
+        <v>-0.3258</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1911</v>
+        <v>0.0012</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3809</v>
+        <v>-0.3271</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1906</v>
@@ -1936,13 +1936,13 @@
         <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.214</v>
+        <v>0.0322</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3303</v>
+        <v>-0.138</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1164</v>
+        <v>0.1702</v>
       </c>
       <c r="V19" t="n">
         <v>-1.267</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1079</v>
+        <v>-1.0117</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6744</v>
+        <v>-0.5783</v>
       </c>
       <c r="F20" t="n">
         <v>-0.4335</v>
@@ -2014,10 +2014,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0551</v>
+        <v>0.0411</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0551</v>
+        <v>0.0411</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7311</v>
+        <v>-1.1367</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4068</v>
+        <v>-1.1184</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3242</v>
+        <v>-0.0183</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6722</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1872</v>
+        <v>0.4072</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1847</v>
+        <v>0.1037</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0024</v>
+        <v>0.3035</v>
       </c>
       <c r="V21" t="n">
         <v>0.3115</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.33</v>
+        <v>-2.2586</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0218</v>
+        <v>-2.9256</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6918</v>
+        <v>0.667</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8369</v>
@@ -2170,13 +2170,13 @@
         <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0566</v>
+        <v>0.128</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0196</v>
+        <v>0.0766</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0762</v>
+        <v>0.0515</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9612</v>
+        <v>-5.2143</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.9548</v>
+        <v>-5.6086</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0064</v>
+        <v>0.3943</v>
       </c>
       <c r="G23" t="n">
         <v>-6.3178</v>
@@ -2248,13 +2248,13 @@
         <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6434</v>
+        <v>1.1035</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6425</v>
+        <v>0.7036</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0008</v>
+        <v>0.3999</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.789099999999998</v>
+        <v>9.071199999999997</v>
       </c>
       <c r="E24" t="n">
         <v>9.2986</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5093</v>
+        <v>-0.2275000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-14.2564</v>
@@ -2326,13 +2326,13 @@
         <v>14.6606</v>
       </c>
       <c r="S24" t="n">
-        <v>11.9983</v>
+        <v>13.2805</v>
       </c>
       <c r="T24" t="n">
-        <v>9.2348</v>
+        <v>9.234599999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7639</v>
+        <v>4.0459</v>
       </c>
       <c r="V24" t="n">
         <v>8.214399999999999</v>
